--- a/plot/sensitivity_phi.xlsx
+++ b/plot/sensitivity_phi.xlsx
@@ -436,32 +436,32 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Unit Cost (元/kWh)</t>
+          <t>LCOE (元/kWh)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Investment Cost (万元)</t>
+          <t>Equipment Investment (万元, one-time)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Grid Cost (万元)</t>
+          <t>Annual Grid Cost (万元/yr)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Connection Cost (万元)</t>
+          <t>Connection Cost (万元, one-time)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Market Revenue (万元)</t>
+          <t>Annual Market Revenue (万元/yr)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Objective (万元)</t>
+          <t>Annualized Objective (万元/yr)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -490,34 +490,34 @@
         <v>0.1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03411922544208271</v>
+        <v>0.2011212020879525</v>
       </c>
       <c r="C2" t="n">
-        <v>13122.12595786683</v>
+        <v>167792.8141298215</v>
       </c>
       <c r="D2" t="n">
-        <v>11749.28398782329</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>5000</v>
       </c>
       <c r="F2" t="n">
-        <v>5548.787676261022</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>24322.62226942561</v>
+        <v>20718.6259613755</v>
       </c>
       <c r="H2" t="n">
-        <v>183.6162828396875</v>
+        <v>74.78175886784675</v>
       </c>
       <c r="I2" t="n">
-        <v>68.71626054961486</v>
+        <v>158.6441210180155</v>
       </c>
       <c r="J2" t="n">
-        <v>55.65231230131448</v>
+        <v>502.2034833580587</v>
       </c>
       <c r="K2" t="n">
-        <v>18.86526009605538</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -525,34 +525,34 @@
         <v>0.2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.03411922544208271</v>
+        <v>0.2011212020879525</v>
       </c>
       <c r="C3" t="n">
-        <v>13122.12595786683</v>
+        <v>167792.8141298215</v>
       </c>
       <c r="D3" t="n">
-        <v>11749.28398782329</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>5000</v>
       </c>
       <c r="F3" t="n">
-        <v>5548.787676261022</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>24322.62226942561</v>
+        <v>20718.6259613755</v>
       </c>
       <c r="H3" t="n">
-        <v>183.6162828396875</v>
+        <v>74.78175886784675</v>
       </c>
       <c r="I3" t="n">
-        <v>68.71626054961486</v>
+        <v>158.6441210180155</v>
       </c>
       <c r="J3" t="n">
-        <v>55.65231230131448</v>
+        <v>502.2034833580587</v>
       </c>
       <c r="K3" t="n">
-        <v>18.86526009605538</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -560,34 +560,34 @@
         <v>0.3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03379929626867933</v>
+        <v>0.2011212020879525</v>
       </c>
       <c r="C4" t="n">
-        <v>13106.53760906378</v>
+        <v>167792.8141298215</v>
       </c>
       <c r="D4" t="n">
-        <v>11749.28398782329</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>5000</v>
       </c>
       <c r="F4" t="n">
-        <v>5658.110705119165</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>24197.71089176456</v>
+        <v>20718.6259613755</v>
       </c>
       <c r="H4" t="n">
-        <v>187.7217931756649</v>
+        <v>74.78175886784675</v>
       </c>
       <c r="I4" t="n">
-        <v>50.68883957922867</v>
+        <v>158.6441210180155</v>
       </c>
       <c r="J4" t="n">
-        <v>74.17576533402961</v>
+        <v>502.2034833580587</v>
       </c>
       <c r="K4" t="n">
-        <v>18.86526009605538</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -595,34 +595,34 @@
         <v>0.4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.03379929626867933</v>
+        <v>0.2011212020879525</v>
       </c>
       <c r="C5" t="n">
-        <v>13106.53760906378</v>
+        <v>167792.8141298215</v>
       </c>
       <c r="D5" t="n">
-        <v>11749.28398782329</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>5000</v>
       </c>
       <c r="F5" t="n">
-        <v>5658.110705119165</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>24197.71089176456</v>
+        <v>20718.6259613755</v>
       </c>
       <c r="H5" t="n">
-        <v>187.7217931756649</v>
+        <v>74.78175886784675</v>
       </c>
       <c r="I5" t="n">
-        <v>50.68883957922867</v>
+        <v>158.6441210180155</v>
       </c>
       <c r="J5" t="n">
-        <v>74.17576533402961</v>
+        <v>502.2034833580587</v>
       </c>
       <c r="K5" t="n">
-        <v>18.86526009605538</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -630,34 +630,34 @@
         <v>0.5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.03379929626867933</v>
+        <v>0.2011212020879525</v>
       </c>
       <c r="C6" t="n">
-        <v>13106.53760906378</v>
+        <v>167792.8141298215</v>
       </c>
       <c r="D6" t="n">
-        <v>11749.28398782329</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>5000</v>
       </c>
       <c r="F6" t="n">
-        <v>5658.110705119165</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>24197.71089176456</v>
+        <v>20718.6259613755</v>
       </c>
       <c r="H6" t="n">
-        <v>187.7217931756649</v>
+        <v>74.78175886784675</v>
       </c>
       <c r="I6" t="n">
-        <v>50.68883957922867</v>
+        <v>158.6441210180155</v>
       </c>
       <c r="J6" t="n">
-        <v>74.17576533402961</v>
+        <v>502.2034833580587</v>
       </c>
       <c r="K6" t="n">
-        <v>18.86526009605538</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -665,34 +665,34 @@
         <v>0.6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.03411922544208271</v>
+        <v>0.2011212020879525</v>
       </c>
       <c r="C7" t="n">
-        <v>13122.12595786683</v>
+        <v>167792.8141298215</v>
       </c>
       <c r="D7" t="n">
-        <v>11749.28398782329</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>5000</v>
       </c>
       <c r="F7" t="n">
-        <v>5548.787676261022</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>24322.62226942561</v>
+        <v>20718.6259613755</v>
       </c>
       <c r="H7" t="n">
-        <v>183.6162828396875</v>
+        <v>74.78175886784675</v>
       </c>
       <c r="I7" t="n">
-        <v>68.71626054961486</v>
+        <v>158.6441210180155</v>
       </c>
       <c r="J7" t="n">
-        <v>55.65231230131448</v>
+        <v>502.2034833580587</v>
       </c>
       <c r="K7" t="n">
-        <v>18.86526009605538</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -700,34 +700,34 @@
         <v>0.7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.03379929626867933</v>
+        <v>0.2011212020879525</v>
       </c>
       <c r="C8" t="n">
-        <v>13106.53760906378</v>
+        <v>167792.8141298215</v>
       </c>
       <c r="D8" t="n">
-        <v>11749.28398782329</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>5000</v>
       </c>
       <c r="F8" t="n">
-        <v>5658.110705119165</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>24197.71089176456</v>
+        <v>20718.6259613755</v>
       </c>
       <c r="H8" t="n">
-        <v>187.7217931756649</v>
+        <v>74.78175886784675</v>
       </c>
       <c r="I8" t="n">
-        <v>50.68883957922867</v>
+        <v>158.6441210180155</v>
       </c>
       <c r="J8" t="n">
-        <v>74.17576533402961</v>
+        <v>502.2034833580587</v>
       </c>
       <c r="K8" t="n">
-        <v>18.86526009605538</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -735,34 +735,34 @@
         <v>0.8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.03379929626867933</v>
+        <v>0.2011212020879525</v>
       </c>
       <c r="C9" t="n">
-        <v>13106.53760906378</v>
+        <v>167792.8141298215</v>
       </c>
       <c r="D9" t="n">
-        <v>11749.28398782329</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>5000</v>
       </c>
       <c r="F9" t="n">
-        <v>5658.110705119165</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>24197.71089176456</v>
+        <v>20718.6259613755</v>
       </c>
       <c r="H9" t="n">
-        <v>187.7217931756649</v>
+        <v>74.78175886784675</v>
       </c>
       <c r="I9" t="n">
-        <v>50.68883957922867</v>
+        <v>158.6441210180155</v>
       </c>
       <c r="J9" t="n">
-        <v>74.17576533402961</v>
+        <v>502.2034833580587</v>
       </c>
       <c r="K9" t="n">
-        <v>18.86526009605538</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -770,34 +770,34 @@
         <v>0.9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.0412756625916272</v>
+        <v>0.192183377673587</v>
       </c>
       <c r="C10" t="n">
-        <v>12125.02052276611</v>
+        <v>160113.9030218765</v>
       </c>
       <c r="D10" t="n">
-        <v>11749.28398782329</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>5000</v>
       </c>
       <c r="F10" t="n">
-        <v>3049.528909828154</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>25824.77560075883</v>
+        <v>19999.27494433461</v>
       </c>
       <c r="H10" t="n">
-        <v>175.2781856043299</v>
+        <v>66.02214850775843</v>
       </c>
       <c r="I10" t="n">
-        <v>49.91286383324546</v>
+        <v>137.2598156696914</v>
       </c>
       <c r="J10" t="n">
-        <v>55.65231230131445</v>
+        <v>528.8177947754265</v>
       </c>
       <c r="K10" t="n">
-        <v>18.86526009605538</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/plot/sensitivity_phi.xlsx
+++ b/plot/sensitivity_phi.xlsx
@@ -490,34 +490,34 @@
         <v>0.1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.2011212020879525</v>
+        <v>0.2482182265340659</v>
       </c>
       <c r="C2" t="n">
-        <v>167792.8141298215</v>
+        <v>76260.24694757526</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>6820.391239989129</v>
       </c>
       <c r="E2" t="n">
         <v>5000</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1540.556581589423</v>
       </c>
       <c r="G2" t="n">
-        <v>20718.6259613755</v>
+        <v>17423.80148265012</v>
       </c>
       <c r="H2" t="n">
-        <v>74.78175886784675</v>
+        <v>42.13356860772264</v>
       </c>
       <c r="I2" t="n">
-        <v>158.6441210180155</v>
+        <v>81.41863723056635</v>
       </c>
       <c r="J2" t="n">
-        <v>502.2034833580587</v>
+        <v>175.2040221266206</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>22.82594123155665</v>
       </c>
     </row>
     <row r="3">
@@ -525,34 +525,34 @@
         <v>0.2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.2011212020879525</v>
+        <v>0.2482182265340659</v>
       </c>
       <c r="C3" t="n">
-        <v>167792.8141298215</v>
+        <v>76260.24694757526</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>6820.391239989129</v>
       </c>
       <c r="E3" t="n">
         <v>5000</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1540.556581589423</v>
       </c>
       <c r="G3" t="n">
-        <v>20718.6259613755</v>
+        <v>17423.80148265012</v>
       </c>
       <c r="H3" t="n">
-        <v>74.78175886784675</v>
+        <v>42.13356860772264</v>
       </c>
       <c r="I3" t="n">
-        <v>158.6441210180155</v>
+        <v>81.41863723056635</v>
       </c>
       <c r="J3" t="n">
-        <v>502.2034833580587</v>
+        <v>175.2040221266206</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>22.82594123155665</v>
       </c>
     </row>
     <row r="4">
@@ -560,34 +560,34 @@
         <v>0.3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.2011212020879525</v>
+        <v>0.2482182265340659</v>
       </c>
       <c r="C4" t="n">
-        <v>167792.8141298215</v>
+        <v>76260.24694757526</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>6820.391239989129</v>
       </c>
       <c r="E4" t="n">
         <v>5000</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1540.556581589423</v>
       </c>
       <c r="G4" t="n">
-        <v>20718.6259613755</v>
+        <v>17423.80148265012</v>
       </c>
       <c r="H4" t="n">
-        <v>74.78175886784675</v>
+        <v>42.13356860772264</v>
       </c>
       <c r="I4" t="n">
-        <v>158.6441210180155</v>
+        <v>81.41863723056635</v>
       </c>
       <c r="J4" t="n">
-        <v>502.2034833580587</v>
+        <v>175.2040221266206</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>22.82594123155665</v>
       </c>
     </row>
     <row r="5">
@@ -595,34 +595,34 @@
         <v>0.4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.2011212020879525</v>
+        <v>0.2482182265340659</v>
       </c>
       <c r="C5" t="n">
-        <v>167792.8141298215</v>
+        <v>76260.24694757526</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>6820.391239989129</v>
       </c>
       <c r="E5" t="n">
         <v>5000</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1540.556581589423</v>
       </c>
       <c r="G5" t="n">
-        <v>20718.6259613755</v>
+        <v>17423.80148265012</v>
       </c>
       <c r="H5" t="n">
-        <v>74.78175886784675</v>
+        <v>42.13356860772264</v>
       </c>
       <c r="I5" t="n">
-        <v>158.6441210180155</v>
+        <v>81.41863723056635</v>
       </c>
       <c r="J5" t="n">
-        <v>502.2034833580587</v>
+        <v>175.2040221266206</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>22.82594123155665</v>
       </c>
     </row>
     <row r="6">
@@ -630,34 +630,34 @@
         <v>0.5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.2011212020879525</v>
+        <v>0.2482182265340659</v>
       </c>
       <c r="C6" t="n">
-        <v>167792.8141298215</v>
+        <v>76260.24694757526</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>6820.391239989129</v>
       </c>
       <c r="E6" t="n">
         <v>5000</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1540.556581589423</v>
       </c>
       <c r="G6" t="n">
-        <v>20718.6259613755</v>
+        <v>17423.80148265012</v>
       </c>
       <c r="H6" t="n">
-        <v>74.78175886784675</v>
+        <v>42.13356860772264</v>
       </c>
       <c r="I6" t="n">
-        <v>158.6441210180155</v>
+        <v>81.41863723056635</v>
       </c>
       <c r="J6" t="n">
-        <v>502.2034833580587</v>
+        <v>175.2040221266206</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>22.82594123155665</v>
       </c>
     </row>
     <row r="7">
@@ -665,34 +665,34 @@
         <v>0.6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.2011212020879525</v>
+        <v>0.2482182265340659</v>
       </c>
       <c r="C7" t="n">
-        <v>167792.8141298215</v>
+        <v>76260.24694757526</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>6820.391239989129</v>
       </c>
       <c r="E7" t="n">
         <v>5000</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1540.556581589423</v>
       </c>
       <c r="G7" t="n">
-        <v>20718.6259613755</v>
+        <v>17423.80148265012</v>
       </c>
       <c r="H7" t="n">
-        <v>74.78175886784675</v>
+        <v>42.13356860772264</v>
       </c>
       <c r="I7" t="n">
-        <v>158.6441210180155</v>
+        <v>81.41863723056635</v>
       </c>
       <c r="J7" t="n">
-        <v>502.2034833580587</v>
+        <v>175.2040221266206</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>22.82594123155665</v>
       </c>
     </row>
     <row r="8">
@@ -700,34 +700,34 @@
         <v>0.7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.2011212020879525</v>
+        <v>0.2482182265340659</v>
       </c>
       <c r="C8" t="n">
-        <v>167792.8141298215</v>
+        <v>76260.24694757526</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>6820.391239989129</v>
       </c>
       <c r="E8" t="n">
         <v>5000</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1540.556581589423</v>
       </c>
       <c r="G8" t="n">
-        <v>20718.6259613755</v>
+        <v>17423.80148265012</v>
       </c>
       <c r="H8" t="n">
-        <v>74.78175886784675</v>
+        <v>42.13356860772264</v>
       </c>
       <c r="I8" t="n">
-        <v>158.6441210180155</v>
+        <v>81.41863723056635</v>
       </c>
       <c r="J8" t="n">
-        <v>502.2034833580587</v>
+        <v>175.2040221266206</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>22.82594123155665</v>
       </c>
     </row>
     <row r="9">
@@ -735,34 +735,34 @@
         <v>0.8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.2011212020879525</v>
+        <v>0.2482182265340659</v>
       </c>
       <c r="C9" t="n">
-        <v>167792.8141298215</v>
+        <v>76260.24694757526</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>6820.391239989129</v>
       </c>
       <c r="E9" t="n">
         <v>5000</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1540.556581589423</v>
       </c>
       <c r="G9" t="n">
-        <v>20718.6259613755</v>
+        <v>17423.80148265012</v>
       </c>
       <c r="H9" t="n">
-        <v>74.78175886784675</v>
+        <v>42.13356860772264</v>
       </c>
       <c r="I9" t="n">
-        <v>158.6441210180155</v>
+        <v>81.41863723056635</v>
       </c>
       <c r="J9" t="n">
-        <v>502.2034833580587</v>
+        <v>175.2040221266206</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>22.82594123155665</v>
       </c>
     </row>
     <row r="10">
@@ -770,34 +770,34 @@
         <v>0.9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.192183377673587</v>
+        <v>0.335569932106325</v>
       </c>
       <c r="C10" t="n">
-        <v>160113.9030218765</v>
+        <v>27317.34000058295</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>10787.06753188883</v>
       </c>
       <c r="E10" t="n">
         <v>5000</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>547.5959888959505</v>
       </c>
       <c r="G10" t="n">
-        <v>19999.27494433461</v>
+        <v>17798.52660119498</v>
       </c>
       <c r="H10" t="n">
-        <v>66.02214850775843</v>
+        <v>4.397287340195575</v>
       </c>
       <c r="I10" t="n">
-        <v>137.2598156696914</v>
+        <v>53.81619258511999</v>
       </c>
       <c r="J10" t="n">
-        <v>528.8177947754265</v>
+        <v>54.00596171599961</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>36.10129696080599</v>
       </c>
     </row>
   </sheetData>

--- a/plot/sensitivity_phi.xlsx
+++ b/plot/sensitivity_phi.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phi Analysis" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="phi Analysis" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,379 +425,557 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Distance (km)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Min Self-consumption Ratio</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Min RE Generation Ratio</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>LCOE (元/kWh)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Equipment Investment (万元, one-time)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Annual Grid Cost (万元/yr)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Connection Cost (万元, one-time)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Annual Market Revenue (万元/yr)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Annualized Objective (万元/yr)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>MIP Gap Target</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>MIP Gap Achieved</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Wind (MW)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>PV (MW)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Storage (MWh)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Grid (MW)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Output Directory</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B2" t="n">
         <v>0.1</v>
       </c>
-      <c r="B2" t="n">
-        <v>0.2482182265340659</v>
-      </c>
       <c r="C2" t="n">
-        <v>76260.24694757526</v>
+        <v>0.3</v>
       </c>
       <c r="D2" t="n">
-        <v>6820.391239989129</v>
+        <v>0.2430882847053844</v>
       </c>
       <c r="E2" t="n">
+        <v>69413.43308752358</v>
+      </c>
+      <c r="F2" t="n">
+        <v>7409.252504752736</v>
+      </c>
+      <c r="G2" t="n">
         <v>5000</v>
       </c>
-      <c r="F2" t="n">
-        <v>1540.556581589423</v>
-      </c>
-      <c r="G2" t="n">
-        <v>17423.80148265012</v>
-      </c>
       <c r="H2" t="n">
-        <v>42.13356860772264</v>
+        <v>2031.840396733106</v>
       </c>
       <c r="I2" t="n">
-        <v>81.41863723056635</v>
+        <v>16879.97776946437</v>
       </c>
       <c r="J2" t="n">
-        <v>175.2040221266206</v>
+        <v>0.01</v>
       </c>
       <c r="K2" t="n">
-        <v>22.82594123155665</v>
+        <v>0.009503602762166835</v>
+      </c>
+      <c r="L2" t="n">
+        <v>40.3269320116765</v>
+      </c>
+      <c r="M2" t="n">
+        <v>77.05182595728435</v>
+      </c>
+      <c r="N2" t="n">
+        <v>145.3611050118403</v>
+      </c>
+      <c r="O2" t="n">
+        <v>24.79669512969457</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>results/sensitivity/phi/phi_0.1</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
+        <v>50</v>
+      </c>
+      <c r="B3" t="n">
         <v>0.2</v>
       </c>
-      <c r="B3" t="n">
-        <v>0.2482182265340659</v>
-      </c>
       <c r="C3" t="n">
-        <v>76260.24694757526</v>
+        <v>0.3</v>
       </c>
       <c r="D3" t="n">
-        <v>6820.391239989129</v>
+        <v>0.2430882847053844</v>
       </c>
       <c r="E3" t="n">
+        <v>69413.43308752358</v>
+      </c>
+      <c r="F3" t="n">
+        <v>7409.252504752736</v>
+      </c>
+      <c r="G3" t="n">
         <v>5000</v>
       </c>
-      <c r="F3" t="n">
-        <v>1540.556581589423</v>
-      </c>
-      <c r="G3" t="n">
-        <v>17423.80148265012</v>
-      </c>
       <c r="H3" t="n">
-        <v>42.13356860772264</v>
+        <v>2031.840396733106</v>
       </c>
       <c r="I3" t="n">
-        <v>81.41863723056635</v>
+        <v>16879.97776946437</v>
       </c>
       <c r="J3" t="n">
-        <v>175.2040221266206</v>
+        <v>0.01</v>
       </c>
       <c r="K3" t="n">
-        <v>22.82594123155665</v>
+        <v>0.009503602762166835</v>
+      </c>
+      <c r="L3" t="n">
+        <v>40.3269320116765</v>
+      </c>
+      <c r="M3" t="n">
+        <v>77.05182595728435</v>
+      </c>
+      <c r="N3" t="n">
+        <v>145.3611050118403</v>
+      </c>
+      <c r="O3" t="n">
+        <v>24.79669512969457</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>results/sensitivity/phi/phi_0.2</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
+        <v>50</v>
+      </c>
+      <c r="B4" t="n">
         <v>0.3</v>
       </c>
-      <c r="B4" t="n">
-        <v>0.2482182265340659</v>
-      </c>
       <c r="C4" t="n">
-        <v>76260.24694757526</v>
+        <v>0.3</v>
       </c>
       <c r="D4" t="n">
-        <v>6820.391239989129</v>
+        <v>0.2430882847053844</v>
       </c>
       <c r="E4" t="n">
+        <v>69413.43308752358</v>
+      </c>
+      <c r="F4" t="n">
+        <v>7409.252504752736</v>
+      </c>
+      <c r="G4" t="n">
         <v>5000</v>
       </c>
-      <c r="F4" t="n">
-        <v>1540.556581589423</v>
-      </c>
-      <c r="G4" t="n">
-        <v>17423.80148265012</v>
-      </c>
       <c r="H4" t="n">
-        <v>42.13356860772264</v>
+        <v>2031.840396733106</v>
       </c>
       <c r="I4" t="n">
-        <v>81.41863723056635</v>
+        <v>16879.97776946437</v>
       </c>
       <c r="J4" t="n">
-        <v>175.2040221266206</v>
+        <v>0.01</v>
       </c>
       <c r="K4" t="n">
-        <v>22.82594123155665</v>
+        <v>0.009503602762166835</v>
+      </c>
+      <c r="L4" t="n">
+        <v>40.3269320116765</v>
+      </c>
+      <c r="M4" t="n">
+        <v>77.05182595728435</v>
+      </c>
+      <c r="N4" t="n">
+        <v>145.3611050118403</v>
+      </c>
+      <c r="O4" t="n">
+        <v>24.79669512969457</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>results/sensitivity/phi/phi_0.3</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
+        <v>50</v>
+      </c>
+      <c r="B5" t="n">
         <v>0.4</v>
       </c>
-      <c r="B5" t="n">
-        <v>0.2482182265340659</v>
-      </c>
       <c r="C5" t="n">
-        <v>76260.24694757526</v>
+        <v>0.3</v>
       </c>
       <c r="D5" t="n">
-        <v>6820.391239989129</v>
+        <v>0.2430882847053844</v>
       </c>
       <c r="E5" t="n">
+        <v>69413.43308752358</v>
+      </c>
+      <c r="F5" t="n">
+        <v>7409.252504752736</v>
+      </c>
+      <c r="G5" t="n">
         <v>5000</v>
       </c>
-      <c r="F5" t="n">
-        <v>1540.556581589423</v>
-      </c>
-      <c r="G5" t="n">
-        <v>17423.80148265012</v>
-      </c>
       <c r="H5" t="n">
-        <v>42.13356860772264</v>
+        <v>2031.840396733106</v>
       </c>
       <c r="I5" t="n">
-        <v>81.41863723056635</v>
+        <v>16879.97776946437</v>
       </c>
       <c r="J5" t="n">
-        <v>175.2040221266206</v>
+        <v>0.01</v>
       </c>
       <c r="K5" t="n">
-        <v>22.82594123155665</v>
+        <v>0.009503602762166835</v>
+      </c>
+      <c r="L5" t="n">
+        <v>40.3269320116765</v>
+      </c>
+      <c r="M5" t="n">
+        <v>77.05182595728435</v>
+      </c>
+      <c r="N5" t="n">
+        <v>145.3611050118403</v>
+      </c>
+      <c r="O5" t="n">
+        <v>24.79669512969457</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>results/sensitivity/phi/phi_0.4</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>50</v>
+      </c>
+      <c r="B6" t="n">
         <v>0.5</v>
       </c>
-      <c r="B6" t="n">
-        <v>0.2482182265340659</v>
-      </c>
       <c r="C6" t="n">
-        <v>76260.24694757526</v>
+        <v>0.3</v>
       </c>
       <c r="D6" t="n">
-        <v>6820.391239989129</v>
+        <v>0.2430882847053844</v>
       </c>
       <c r="E6" t="n">
+        <v>69413.43308752358</v>
+      </c>
+      <c r="F6" t="n">
+        <v>7409.252504752736</v>
+      </c>
+      <c r="G6" t="n">
         <v>5000</v>
       </c>
-      <c r="F6" t="n">
-        <v>1540.556581589423</v>
-      </c>
-      <c r="G6" t="n">
-        <v>17423.80148265012</v>
-      </c>
       <c r="H6" t="n">
-        <v>42.13356860772264</v>
+        <v>2031.840396733106</v>
       </c>
       <c r="I6" t="n">
-        <v>81.41863723056635</v>
+        <v>16879.97776946437</v>
       </c>
       <c r="J6" t="n">
-        <v>175.2040221266206</v>
+        <v>0.01</v>
       </c>
       <c r="K6" t="n">
-        <v>22.82594123155665</v>
+        <v>0.009503602762166835</v>
+      </c>
+      <c r="L6" t="n">
+        <v>40.3269320116765</v>
+      </c>
+      <c r="M6" t="n">
+        <v>77.05182595728435</v>
+      </c>
+      <c r="N6" t="n">
+        <v>145.3611050118403</v>
+      </c>
+      <c r="O6" t="n">
+        <v>24.79669512969457</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>results/sensitivity/phi/phi_0.5</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
+        <v>50</v>
+      </c>
+      <c r="B7" t="n">
         <v>0.6</v>
       </c>
-      <c r="B7" t="n">
-        <v>0.2482182265340659</v>
-      </c>
       <c r="C7" t="n">
-        <v>76260.24694757526</v>
+        <v>0.3</v>
       </c>
       <c r="D7" t="n">
-        <v>6820.391239989129</v>
+        <v>0.2430882847053844</v>
       </c>
       <c r="E7" t="n">
+        <v>69413.43308752358</v>
+      </c>
+      <c r="F7" t="n">
+        <v>7409.252504752736</v>
+      </c>
+      <c r="G7" t="n">
         <v>5000</v>
       </c>
-      <c r="F7" t="n">
-        <v>1540.556581589423</v>
-      </c>
-      <c r="G7" t="n">
-        <v>17423.80148265012</v>
-      </c>
       <c r="H7" t="n">
-        <v>42.13356860772264</v>
+        <v>2031.840396733106</v>
       </c>
       <c r="I7" t="n">
-        <v>81.41863723056635</v>
+        <v>16879.97776946437</v>
       </c>
       <c r="J7" t="n">
-        <v>175.2040221266206</v>
+        <v>0.01</v>
       </c>
       <c r="K7" t="n">
-        <v>22.82594123155665</v>
+        <v>0.009503602762166835</v>
+      </c>
+      <c r="L7" t="n">
+        <v>40.3269320116765</v>
+      </c>
+      <c r="M7" t="n">
+        <v>77.05182595728435</v>
+      </c>
+      <c r="N7" t="n">
+        <v>145.3611050118403</v>
+      </c>
+      <c r="O7" t="n">
+        <v>24.79669512969457</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>results/sensitivity/phi/phi_0.6</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
+        <v>50</v>
+      </c>
+      <c r="B8" t="n">
         <v>0.7</v>
       </c>
-      <c r="B8" t="n">
-        <v>0.2482182265340659</v>
-      </c>
       <c r="C8" t="n">
-        <v>76260.24694757526</v>
+        <v>0.3</v>
       </c>
       <c r="D8" t="n">
-        <v>6820.391239989129</v>
+        <v>0.2430882847053844</v>
       </c>
       <c r="E8" t="n">
+        <v>69413.43308752358</v>
+      </c>
+      <c r="F8" t="n">
+        <v>7409.252504752736</v>
+      </c>
+      <c r="G8" t="n">
         <v>5000</v>
       </c>
-      <c r="F8" t="n">
-        <v>1540.556581589423</v>
-      </c>
-      <c r="G8" t="n">
-        <v>17423.80148265012</v>
-      </c>
       <c r="H8" t="n">
-        <v>42.13356860772264</v>
+        <v>2031.840396733106</v>
       </c>
       <c r="I8" t="n">
-        <v>81.41863723056635</v>
+        <v>16879.97776946437</v>
       </c>
       <c r="J8" t="n">
-        <v>175.2040221266206</v>
+        <v>0.01</v>
       </c>
       <c r="K8" t="n">
-        <v>22.82594123155665</v>
+        <v>0.009503602762166835</v>
+      </c>
+      <c r="L8" t="n">
+        <v>40.3269320116765</v>
+      </c>
+      <c r="M8" t="n">
+        <v>77.05182595728435</v>
+      </c>
+      <c r="N8" t="n">
+        <v>145.3611050118403</v>
+      </c>
+      <c r="O8" t="n">
+        <v>24.79669512969457</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>results/sensitivity/phi/phi_0.7</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
+        <v>50</v>
+      </c>
+      <c r="B9" t="n">
         <v>0.8</v>
       </c>
-      <c r="B9" t="n">
-        <v>0.2482182265340659</v>
-      </c>
       <c r="C9" t="n">
-        <v>76260.24694757526</v>
+        <v>0.3</v>
       </c>
       <c r="D9" t="n">
-        <v>6820.391239989129</v>
+        <v>0.2430882847053844</v>
       </c>
       <c r="E9" t="n">
+        <v>69413.43308752358</v>
+      </c>
+      <c r="F9" t="n">
+        <v>7409.252504752736</v>
+      </c>
+      <c r="G9" t="n">
         <v>5000</v>
       </c>
-      <c r="F9" t="n">
-        <v>1540.556581589423</v>
-      </c>
-      <c r="G9" t="n">
-        <v>17423.80148265012</v>
-      </c>
       <c r="H9" t="n">
-        <v>42.13356860772264</v>
+        <v>2031.840396733106</v>
       </c>
       <c r="I9" t="n">
-        <v>81.41863723056635</v>
+        <v>16879.97776946437</v>
       </c>
       <c r="J9" t="n">
-        <v>175.2040221266206</v>
+        <v>0.01</v>
       </c>
       <c r="K9" t="n">
-        <v>22.82594123155665</v>
+        <v>0.009503602762166835</v>
+      </c>
+      <c r="L9" t="n">
+        <v>40.3269320116765</v>
+      </c>
+      <c r="M9" t="n">
+        <v>77.05182595728435</v>
+      </c>
+      <c r="N9" t="n">
+        <v>145.3611050118403</v>
+      </c>
+      <c r="O9" t="n">
+        <v>24.79669512969457</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>results/sensitivity/phi/phi_0.8</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
+        <v>50</v>
+      </c>
+      <c r="B10" t="n">
         <v>0.9</v>
       </c>
-      <c r="B10" t="n">
-        <v>0.335569932106325</v>
-      </c>
       <c r="C10" t="n">
-        <v>27317.34000058295</v>
+        <v>0.3</v>
       </c>
       <c r="D10" t="n">
-        <v>10787.06753188883</v>
+        <v>0.3352549506121519</v>
       </c>
       <c r="E10" t="n">
+        <v>15512.35128008481</v>
+      </c>
+      <c r="F10" t="n">
+        <v>10762.95192628893</v>
+      </c>
+      <c r="G10" t="n">
         <v>5000</v>
       </c>
-      <c r="F10" t="n">
-        <v>547.5959888959505</v>
-      </c>
-      <c r="G10" t="n">
-        <v>17798.52660119498</v>
-      </c>
       <c r="H10" t="n">
-        <v>4.397287340195575</v>
+        <v>62.10545927190775</v>
       </c>
       <c r="I10" t="n">
-        <v>53.81619258511999</v>
+        <v>17154.0245951606</v>
       </c>
       <c r="J10" t="n">
-        <v>54.00596171599961</v>
+        <v>0.01</v>
       </c>
       <c r="K10" t="n">
-        <v>36.10129696080599</v>
+        <v>0.00998303516494563</v>
+      </c>
+      <c r="L10" t="n">
+        <v>4.738119514719224</v>
+      </c>
+      <c r="M10" t="n">
+        <v>19.90574856371547</v>
+      </c>
+      <c r="N10" t="n">
+        <v>41.77005291217218</v>
+      </c>
+      <c r="O10" t="n">
+        <v>36.02058877606736</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>results/sensitivity/phi/phi_0.9</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/plot/sensitivity_phi.xlsx
+++ b/plot/sensitivity_phi.xlsx
@@ -521,40 +521,40 @@
         <v>0.3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2430882847053844</v>
+        <v>0.3112591114115704</v>
       </c>
       <c r="E2" t="n">
-        <v>69413.43308752358</v>
+        <v>38317.54338179057</v>
       </c>
       <c r="F2" t="n">
-        <v>7409.252504752736</v>
+        <v>8964</v>
       </c>
       <c r="G2" t="n">
         <v>5000</v>
       </c>
       <c r="H2" t="n">
-        <v>2031.840396733106</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>16879.97776946437</v>
+        <v>17553.54068027696</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.009503602762166835</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>40.3269320116765</v>
+        <v>13.69260090255952</v>
       </c>
       <c r="M2" t="n">
-        <v>77.05182595728435</v>
+        <v>37.32662377131042</v>
       </c>
       <c r="N2" t="n">
-        <v>145.3611050118403</v>
+        <v>123.6266380590782</v>
       </c>
       <c r="O2" t="n">
-        <v>24.79669512969457</v>
+        <v>30</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -573,40 +573,40 @@
         <v>0.3</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2430882847053844</v>
+        <v>0.3112591114115704</v>
       </c>
       <c r="E3" t="n">
-        <v>69413.43308752358</v>
+        <v>38317.54338179057</v>
       </c>
       <c r="F3" t="n">
-        <v>7409.252504752736</v>
+        <v>8964</v>
       </c>
       <c r="G3" t="n">
         <v>5000</v>
       </c>
       <c r="H3" t="n">
-        <v>2031.840396733106</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>16879.97776946437</v>
+        <v>17553.54068027696</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="K3" t="n">
-        <v>0.009503602762166835</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>40.3269320116765</v>
+        <v>13.69260090255952</v>
       </c>
       <c r="M3" t="n">
-        <v>77.05182595728435</v>
+        <v>37.32662377131042</v>
       </c>
       <c r="N3" t="n">
-        <v>145.3611050118403</v>
+        <v>123.6266380590782</v>
       </c>
       <c r="O3" t="n">
-        <v>24.79669512969457</v>
+        <v>30</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -625,40 +625,40 @@
         <v>0.3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2430882847053844</v>
+        <v>0.3112591114115704</v>
       </c>
       <c r="E4" t="n">
-        <v>69413.43308752358</v>
+        <v>38317.54338179057</v>
       </c>
       <c r="F4" t="n">
-        <v>7409.252504752736</v>
+        <v>8964</v>
       </c>
       <c r="G4" t="n">
         <v>5000</v>
       </c>
       <c r="H4" t="n">
-        <v>2031.840396733106</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>16879.97776946437</v>
+        <v>17553.54068027696</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009503602762166835</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>40.3269320116765</v>
+        <v>13.69260090255952</v>
       </c>
       <c r="M4" t="n">
-        <v>77.05182595728435</v>
+        <v>37.32662377131042</v>
       </c>
       <c r="N4" t="n">
-        <v>145.3611050118403</v>
+        <v>123.6266380590782</v>
       </c>
       <c r="O4" t="n">
-        <v>24.79669512969457</v>
+        <v>30</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -677,40 +677,40 @@
         <v>0.3</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2430882847053844</v>
+        <v>0.3112591114115704</v>
       </c>
       <c r="E5" t="n">
-        <v>69413.43308752358</v>
+        <v>38317.54338179057</v>
       </c>
       <c r="F5" t="n">
-        <v>7409.252504752736</v>
+        <v>8964</v>
       </c>
       <c r="G5" t="n">
         <v>5000</v>
       </c>
       <c r="H5" t="n">
-        <v>2031.840396733106</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>16879.97776946437</v>
+        <v>17553.54068027696</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="K5" t="n">
-        <v>0.009503602762166835</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>40.3269320116765</v>
+        <v>13.69260090255952</v>
       </c>
       <c r="M5" t="n">
-        <v>77.05182595728435</v>
+        <v>37.32662377131042</v>
       </c>
       <c r="N5" t="n">
-        <v>145.3611050118403</v>
+        <v>123.6266380590782</v>
       </c>
       <c r="O5" t="n">
-        <v>24.79669512969457</v>
+        <v>30</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -729,40 +729,40 @@
         <v>0.3</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2430882847053844</v>
+        <v>0.3112591114115704</v>
       </c>
       <c r="E6" t="n">
-        <v>69413.43308752358</v>
+        <v>38317.54338179057</v>
       </c>
       <c r="F6" t="n">
-        <v>7409.252504752736</v>
+        <v>8964</v>
       </c>
       <c r="G6" t="n">
         <v>5000</v>
       </c>
       <c r="H6" t="n">
-        <v>2031.840396733106</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>16879.97776946437</v>
+        <v>17553.54068027696</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="K6" t="n">
-        <v>0.009503602762166835</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>40.3269320116765</v>
+        <v>13.69260090255952</v>
       </c>
       <c r="M6" t="n">
-        <v>77.05182595728435</v>
+        <v>37.32662377131042</v>
       </c>
       <c r="N6" t="n">
-        <v>145.3611050118403</v>
+        <v>123.6266380590782</v>
       </c>
       <c r="O6" t="n">
-        <v>24.79669512969457</v>
+        <v>30</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -781,40 +781,40 @@
         <v>0.3</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2430882847053844</v>
+        <v>0.3112591114115704</v>
       </c>
       <c r="E7" t="n">
-        <v>69413.43308752358</v>
+        <v>38317.54338179057</v>
       </c>
       <c r="F7" t="n">
-        <v>7409.252504752736</v>
+        <v>8964</v>
       </c>
       <c r="G7" t="n">
         <v>5000</v>
       </c>
       <c r="H7" t="n">
-        <v>2031.840396733106</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>16879.97776946437</v>
+        <v>17553.54068027696</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.009503602762166835</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>40.3269320116765</v>
+        <v>13.69260090255952</v>
       </c>
       <c r="M7" t="n">
-        <v>77.05182595728435</v>
+        <v>37.32662377131042</v>
       </c>
       <c r="N7" t="n">
-        <v>145.3611050118403</v>
+        <v>123.6266380590782</v>
       </c>
       <c r="O7" t="n">
-        <v>24.79669512969457</v>
+        <v>30</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -833,40 +833,40 @@
         <v>0.3</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2430882847053844</v>
+        <v>0.3112591114115704</v>
       </c>
       <c r="E8" t="n">
-        <v>69413.43308752358</v>
+        <v>38317.54338179057</v>
       </c>
       <c r="F8" t="n">
-        <v>7409.252504752736</v>
+        <v>8964</v>
       </c>
       <c r="G8" t="n">
         <v>5000</v>
       </c>
       <c r="H8" t="n">
-        <v>2031.840396733106</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>16879.97776946437</v>
+        <v>17553.54068027696</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.009503602762166835</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>40.3269320116765</v>
+        <v>13.69260090255952</v>
       </c>
       <c r="M8" t="n">
-        <v>77.05182595728435</v>
+        <v>37.32662377131042</v>
       </c>
       <c r="N8" t="n">
-        <v>145.3611050118403</v>
+        <v>123.6266380590782</v>
       </c>
       <c r="O8" t="n">
-        <v>24.79669512969457</v>
+        <v>30</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -885,40 +885,40 @@
         <v>0.3</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2430882847053844</v>
+        <v>0.3112591114115704</v>
       </c>
       <c r="E9" t="n">
-        <v>69413.43308752358</v>
+        <v>38317.54338179057</v>
       </c>
       <c r="F9" t="n">
-        <v>7409.252504752736</v>
+        <v>8964</v>
       </c>
       <c r="G9" t="n">
         <v>5000</v>
       </c>
       <c r="H9" t="n">
-        <v>2031.840396733106</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>16879.97776946437</v>
+        <v>17553.54068027696</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.009503602762166835</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>40.3269320116765</v>
+        <v>13.69260090255952</v>
       </c>
       <c r="M9" t="n">
-        <v>77.05182595728435</v>
+        <v>37.32662377131042</v>
       </c>
       <c r="N9" t="n">
-        <v>145.3611050118403</v>
+        <v>123.6266380590782</v>
       </c>
       <c r="O9" t="n">
-        <v>24.79669512969457</v>
+        <v>30</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -937,40 +937,40 @@
         <v>0.3</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3352549506121519</v>
+        <v>0.3112591114115704</v>
       </c>
       <c r="E10" t="n">
-        <v>15512.35128008481</v>
+        <v>38317.54338179057</v>
       </c>
       <c r="F10" t="n">
-        <v>10762.95192628893</v>
+        <v>8964</v>
       </c>
       <c r="G10" t="n">
         <v>5000</v>
       </c>
       <c r="H10" t="n">
-        <v>62.10545927190775</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>17154.0245951606</v>
+        <v>17553.54068027696</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="K10" t="n">
-        <v>0.00998303516494563</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>4.738119514719224</v>
+        <v>13.69260090255952</v>
       </c>
       <c r="M10" t="n">
-        <v>19.90574856371547</v>
+        <v>37.32662377131042</v>
       </c>
       <c r="N10" t="n">
-        <v>41.77005291217218</v>
+        <v>123.6266380590782</v>
       </c>
       <c r="O10" t="n">
-        <v>36.02058877606736</v>
+        <v>30</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>

--- a/plot/sensitivity_phi.xlsx
+++ b/plot/sensitivity_phi.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:R10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,55 +456,65 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Annual Grid Demand Charge (万元/yr)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Annual Grid Energy Cost (万元/yr)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Annual Grid Cost (万元/yr)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Connection Cost (万元, one-time)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Annual Market Revenue (万元/yr)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Annualized Objective (万元/yr)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>MIP Gap Target</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>MIP Gap Achieved</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Wind (MW)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>PV (MW)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Storage (MWh)</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Grid (MW)</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Output Directory</t>
         </is>
@@ -521,42 +531,48 @@
         <v>0.3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3112591114115704</v>
+        <v>0.3845448868032644</v>
       </c>
       <c r="E2" t="n">
-        <v>38317.54338179057</v>
+        <v>67074.19337427949</v>
       </c>
       <c r="F2" t="n">
-        <v>8964</v>
+        <v>3736.8</v>
       </c>
       <c r="G2" t="n">
+        <v>4673.487665886038</v>
+      </c>
+      <c r="H2" t="n">
+        <v>8410.287665886037</v>
+      </c>
+      <c r="I2" t="n">
         <v>5000</v>
       </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>17553.54068027696</v>
-      </c>
       <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>16830.68287943381</v>
+      </c>
+      <c r="L2" t="n">
         <v>0.05</v>
       </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>13.69260090255952</v>
-      </c>
       <c r="M2" t="n">
-        <v>37.32662377131042</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>123.6266380590782</v>
+        <v>79.39508302539429</v>
       </c>
       <c r="O2" t="n">
-        <v>30</v>
-      </c>
-      <c r="P2" t="inlineStr">
+        <v>57.92667956937272</v>
+      </c>
+      <c r="P2" t="n">
+        <v>8.927597921540723</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>60</v>
+      </c>
+      <c r="R2" t="inlineStr">
         <is>
           <t>results/sensitivity/phi/phi_0.1</t>
         </is>
@@ -573,42 +589,48 @@
         <v>0.3</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3112591114115704</v>
+        <v>0.3845448868032644</v>
       </c>
       <c r="E3" t="n">
-        <v>38317.54338179057</v>
+        <v>67074.19337427949</v>
       </c>
       <c r="F3" t="n">
-        <v>8964</v>
+        <v>3736.8</v>
       </c>
       <c r="G3" t="n">
+        <v>4673.487665886038</v>
+      </c>
+      <c r="H3" t="n">
+        <v>8410.287665886037</v>
+      </c>
+      <c r="I3" t="n">
         <v>5000</v>
       </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>17553.54068027696</v>
-      </c>
       <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>16830.68287943381</v>
+      </c>
+      <c r="L3" t="n">
         <v>0.05</v>
       </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>13.69260090255952</v>
-      </c>
       <c r="M3" t="n">
-        <v>37.32662377131042</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>123.6266380590782</v>
+        <v>79.39508302539429</v>
       </c>
       <c r="O3" t="n">
-        <v>30</v>
-      </c>
-      <c r="P3" t="inlineStr">
+        <v>57.92667956937272</v>
+      </c>
+      <c r="P3" t="n">
+        <v>8.927597921540723</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>60</v>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>results/sensitivity/phi/phi_0.2</t>
         </is>
@@ -625,42 +647,48 @@
         <v>0.3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3112591114115704</v>
+        <v>0.3845448868032644</v>
       </c>
       <c r="E4" t="n">
-        <v>38317.54338179057</v>
+        <v>67074.19337427949</v>
       </c>
       <c r="F4" t="n">
-        <v>8964</v>
+        <v>3736.8</v>
       </c>
       <c r="G4" t="n">
+        <v>4673.487665886038</v>
+      </c>
+      <c r="H4" t="n">
+        <v>8410.287665886037</v>
+      </c>
+      <c r="I4" t="n">
         <v>5000</v>
       </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>17553.54068027696</v>
-      </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>16830.68287943381</v>
+      </c>
+      <c r="L4" t="n">
         <v>0.05</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>13.69260090255952</v>
-      </c>
       <c r="M4" t="n">
-        <v>37.32662377131042</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>123.6266380590782</v>
+        <v>79.39508302539429</v>
       </c>
       <c r="O4" t="n">
-        <v>30</v>
-      </c>
-      <c r="P4" t="inlineStr">
+        <v>57.92667956937272</v>
+      </c>
+      <c r="P4" t="n">
+        <v>8.927597921540723</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>60</v>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>results/sensitivity/phi/phi_0.3</t>
         </is>
@@ -677,42 +705,48 @@
         <v>0.3</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3112591114115704</v>
+        <v>0.3845448868032644</v>
       </c>
       <c r="E5" t="n">
-        <v>38317.54338179057</v>
+        <v>67074.19337427951</v>
       </c>
       <c r="F5" t="n">
-        <v>8964</v>
+        <v>3736.8</v>
       </c>
       <c r="G5" t="n">
+        <v>4673.487665886037</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8410.287665886037</v>
+      </c>
+      <c r="I5" t="n">
         <v>5000</v>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>17553.54068027696</v>
-      </c>
       <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>16830.6828794338</v>
+      </c>
+      <c r="L5" t="n">
         <v>0.05</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>13.69260090255952</v>
-      </c>
       <c r="M5" t="n">
-        <v>37.32662377131042</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>123.6266380590782</v>
+        <v>79.3950830253943</v>
       </c>
       <c r="O5" t="n">
-        <v>30</v>
-      </c>
-      <c r="P5" t="inlineStr">
+        <v>57.92667956937272</v>
+      </c>
+      <c r="P5" t="n">
+        <v>8.927597921540729</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>60</v>
+      </c>
+      <c r="R5" t="inlineStr">
         <is>
           <t>results/sensitivity/phi/phi_0.4</t>
         </is>
@@ -729,42 +763,48 @@
         <v>0.3</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3112591114115704</v>
+        <v>0.3845448868032644</v>
       </c>
       <c r="E6" t="n">
-        <v>38317.54338179057</v>
+        <v>67074.19337427949</v>
       </c>
       <c r="F6" t="n">
-        <v>8964</v>
+        <v>3736.8</v>
       </c>
       <c r="G6" t="n">
+        <v>4673.487665886038</v>
+      </c>
+      <c r="H6" t="n">
+        <v>8410.287665886037</v>
+      </c>
+      <c r="I6" t="n">
         <v>5000</v>
       </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>17553.54068027696</v>
-      </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>16830.68287943381</v>
+      </c>
+      <c r="L6" t="n">
         <v>0.05</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>13.69260090255952</v>
-      </c>
       <c r="M6" t="n">
-        <v>37.32662377131042</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>123.6266380590782</v>
+        <v>79.39508302539429</v>
       </c>
       <c r="O6" t="n">
-        <v>30</v>
-      </c>
-      <c r="P6" t="inlineStr">
+        <v>57.92667956937272</v>
+      </c>
+      <c r="P6" t="n">
+        <v>8.927597921540723</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>60</v>
+      </c>
+      <c r="R6" t="inlineStr">
         <is>
           <t>results/sensitivity/phi/phi_0.5</t>
         </is>
@@ -781,42 +821,48 @@
         <v>0.3</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3112591114115704</v>
+        <v>0.3845448868032644</v>
       </c>
       <c r="E7" t="n">
-        <v>38317.54338179057</v>
+        <v>67074.19337427949</v>
       </c>
       <c r="F7" t="n">
-        <v>8964</v>
+        <v>3736.8</v>
       </c>
       <c r="G7" t="n">
+        <v>4673.487665886038</v>
+      </c>
+      <c r="H7" t="n">
+        <v>8410.287665886037</v>
+      </c>
+      <c r="I7" t="n">
         <v>5000</v>
       </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>17553.54068027696</v>
-      </c>
       <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>16830.68287943381</v>
+      </c>
+      <c r="L7" t="n">
         <v>0.05</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>13.69260090255952</v>
-      </c>
       <c r="M7" t="n">
-        <v>37.32662377131042</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>123.6266380590782</v>
+        <v>79.39508302539429</v>
       </c>
       <c r="O7" t="n">
-        <v>30</v>
-      </c>
-      <c r="P7" t="inlineStr">
+        <v>57.92667956937272</v>
+      </c>
+      <c r="P7" t="n">
+        <v>8.927597921540723</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>60</v>
+      </c>
+      <c r="R7" t="inlineStr">
         <is>
           <t>results/sensitivity/phi/phi_0.6</t>
         </is>
@@ -833,42 +879,48 @@
         <v>0.3</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3112591114115704</v>
+        <v>0.3845448868032644</v>
       </c>
       <c r="E8" t="n">
-        <v>38317.54338179057</v>
+        <v>67074.19337427949</v>
       </c>
       <c r="F8" t="n">
-        <v>8964</v>
+        <v>3736.8</v>
       </c>
       <c r="G8" t="n">
+        <v>4673.487665886038</v>
+      </c>
+      <c r="H8" t="n">
+        <v>8410.287665886037</v>
+      </c>
+      <c r="I8" t="n">
         <v>5000</v>
       </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>17553.54068027696</v>
-      </c>
       <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>16830.68287943382</v>
+      </c>
+      <c r="L8" t="n">
         <v>0.05</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>13.69260090255952</v>
-      </c>
       <c r="M8" t="n">
-        <v>37.32662377131042</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>123.6266380590782</v>
+        <v>79.39508302539429</v>
       </c>
       <c r="O8" t="n">
-        <v>30</v>
-      </c>
-      <c r="P8" t="inlineStr">
+        <v>57.92667956937272</v>
+      </c>
+      <c r="P8" t="n">
+        <v>8.927597921540723</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>60</v>
+      </c>
+      <c r="R8" t="inlineStr">
         <is>
           <t>results/sensitivity/phi/phi_0.7</t>
         </is>
@@ -885,42 +937,48 @@
         <v>0.3</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3112591114115704</v>
+        <v>0.3845448868032644</v>
       </c>
       <c r="E9" t="n">
-        <v>38317.54338179057</v>
+        <v>67074.19337427949</v>
       </c>
       <c r="F9" t="n">
-        <v>8964</v>
+        <v>3736.8</v>
       </c>
       <c r="G9" t="n">
+        <v>4673.487665886038</v>
+      </c>
+      <c r="H9" t="n">
+        <v>8410.287665886037</v>
+      </c>
+      <c r="I9" t="n">
         <v>5000</v>
       </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>17553.54068027696</v>
-      </c>
       <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>16830.68287943381</v>
+      </c>
+      <c r="L9" t="n">
         <v>0.05</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>13.69260090255952</v>
-      </c>
       <c r="M9" t="n">
-        <v>37.32662377131042</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>123.6266380590782</v>
+        <v>79.39508302539429</v>
       </c>
       <c r="O9" t="n">
-        <v>30</v>
-      </c>
-      <c r="P9" t="inlineStr">
+        <v>57.92667956937272</v>
+      </c>
+      <c r="P9" t="n">
+        <v>8.927597921540723</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>60</v>
+      </c>
+      <c r="R9" t="inlineStr">
         <is>
           <t>results/sensitivity/phi/phi_0.8</t>
         </is>
@@ -937,42 +995,48 @@
         <v>0.3</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3112591114115704</v>
+        <v>0.3845448868032644</v>
       </c>
       <c r="E10" t="n">
-        <v>38317.54338179057</v>
+        <v>67074.19337427949</v>
       </c>
       <c r="F10" t="n">
-        <v>8964</v>
+        <v>3736.8</v>
       </c>
       <c r="G10" t="n">
+        <v>4673.487665886038</v>
+      </c>
+      <c r="H10" t="n">
+        <v>8410.287665886037</v>
+      </c>
+      <c r="I10" t="n">
         <v>5000</v>
       </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>17553.54068027696</v>
-      </c>
       <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>16830.68287943381</v>
+      </c>
+      <c r="L10" t="n">
         <v>0.05</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>13.69260090255952</v>
-      </c>
       <c r="M10" t="n">
-        <v>37.32662377131042</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>123.6266380590782</v>
+        <v>79.39508302539429</v>
       </c>
       <c r="O10" t="n">
-        <v>30</v>
-      </c>
-      <c r="P10" t="inlineStr">
+        <v>57.92667956937272</v>
+      </c>
+      <c r="P10" t="n">
+        <v>8.927597921540723</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>60</v>
+      </c>
+      <c r="R10" t="inlineStr">
         <is>
           <t>results/sensitivity/phi/phi_0.9</t>
         </is>

--- a/plot/sensitivity_phi.xlsx
+++ b/plot/sensitivity_phi.xlsx
@@ -531,19 +531,19 @@
         <v>0.3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3845448868032644</v>
+        <v>0.8234669252399083</v>
       </c>
       <c r="E2" t="n">
-        <v>67074.19337427949</v>
+        <v>195447.0087164791</v>
       </c>
       <c r="F2" t="n">
-        <v>3736.8</v>
+        <v>5313.6</v>
       </c>
       <c r="G2" t="n">
-        <v>4673.487665886038</v>
+        <v>9622.454013613658</v>
       </c>
       <c r="H2" t="n">
-        <v>8410.287665886037</v>
+        <v>14936.05401361366</v>
       </c>
       <c r="I2" t="n">
         <v>5000</v>
@@ -552,7 +552,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>16830.68287943381</v>
+        <v>38354.18682574639</v>
       </c>
       <c r="L2" t="n">
         <v>0.05</v>
@@ -561,13 +561,13 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>79.39508302539429</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>57.92667956937272</v>
+        <v>486.8175217911977</v>
       </c>
       <c r="P2" t="n">
-        <v>8.927597921540723</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>60</v>
@@ -589,19 +589,19 @@
         <v>0.3</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3845448868032644</v>
+        <v>0.6345907738150711</v>
       </c>
       <c r="E3" t="n">
-        <v>67074.19337427949</v>
+        <v>98083.50435823954</v>
       </c>
       <c r="F3" t="n">
-        <v>3736.8</v>
+        <v>5313.6</v>
       </c>
       <c r="G3" t="n">
-        <v>4673.487665886038</v>
+        <v>9622.454013613655</v>
       </c>
       <c r="H3" t="n">
-        <v>8410.287665886037</v>
+        <v>14936.05401361366</v>
       </c>
       <c r="I3" t="n">
         <v>5000</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>16830.68287943381</v>
+        <v>26979.25291819702</v>
       </c>
       <c r="L3" t="n">
         <v>0.05</v>
@@ -619,13 +619,13 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>79.39508302539429</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>57.92667956937272</v>
+        <v>243.4087608955989</v>
       </c>
       <c r="P3" t="n">
-        <v>8.927597921540723</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>60</v>
@@ -647,19 +647,19 @@
         <v>0.3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3845448868032644</v>
+        <v>0.5716320566734585</v>
       </c>
       <c r="E4" t="n">
-        <v>67074.19337427949</v>
+        <v>65629.00290549293</v>
       </c>
       <c r="F4" t="n">
-        <v>3736.8</v>
+        <v>5313.6</v>
       </c>
       <c r="G4" t="n">
-        <v>4673.487665886038</v>
+        <v>9622.454013613651</v>
       </c>
       <c r="H4" t="n">
-        <v>8410.287665886037</v>
+        <v>14936.05401361365</v>
       </c>
       <c r="I4" t="n">
         <v>5000</v>
@@ -668,7 +668,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>16830.68287943381</v>
+        <v>23187.60828234725</v>
       </c>
       <c r="L4" t="n">
         <v>0.05</v>
@@ -677,13 +677,13 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>79.39508302539429</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>57.92667956937272</v>
+        <v>162.2725072637323</v>
       </c>
       <c r="P4" t="n">
-        <v>8.927597921540723</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>60</v>
@@ -705,19 +705,19 @@
         <v>0.3</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3845448868032644</v>
+        <v>0.5401526981026531</v>
       </c>
       <c r="E5" t="n">
-        <v>67074.19337427951</v>
+        <v>49401.75217911977</v>
       </c>
       <c r="F5" t="n">
-        <v>3736.8</v>
+        <v>5313.6</v>
       </c>
       <c r="G5" t="n">
-        <v>4673.487665886037</v>
+        <v>9622.454013613675</v>
       </c>
       <c r="H5" t="n">
-        <v>8410.287665886037</v>
+        <v>14936.05401361368</v>
       </c>
       <c r="I5" t="n">
         <v>5000</v>
@@ -726,7 +726,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>16830.6828794338</v>
+        <v>21291.78596442237</v>
       </c>
       <c r="L5" t="n">
         <v>0.05</v>
@@ -735,13 +735,13 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>79.3950830253943</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>57.92667956937272</v>
+        <v>121.7043804477994</v>
       </c>
       <c r="P5" t="n">
-        <v>8.927597921540729</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>60</v>
@@ -763,19 +763,19 @@
         <v>0.3</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3845448868032644</v>
+        <v>0.5212650829601693</v>
       </c>
       <c r="E6" t="n">
-        <v>67074.19337427949</v>
+        <v>39665.40174329598</v>
       </c>
       <c r="F6" t="n">
-        <v>3736.8</v>
+        <v>5313.6</v>
       </c>
       <c r="G6" t="n">
-        <v>4673.487665886038</v>
+        <v>9622.454013613655</v>
       </c>
       <c r="H6" t="n">
-        <v>8410.287665886037</v>
+        <v>14936.05401361366</v>
       </c>
       <c r="I6" t="n">
         <v>5000</v>
@@ -784,7 +784,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>16830.68287943381</v>
+        <v>20154.29257366744</v>
       </c>
       <c r="L6" t="n">
         <v>0.05</v>
@@ -793,13 +793,13 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>79.39508302539429</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>57.92667956937272</v>
+        <v>97.36350435823995</v>
       </c>
       <c r="P6" t="n">
-        <v>8.927597921540723</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>60</v>
@@ -821,19 +821,19 @@
         <v>0.3</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3845448868032644</v>
+        <v>0.5086733395318465</v>
       </c>
       <c r="E7" t="n">
-        <v>67074.19337427949</v>
+        <v>33174.50145274647</v>
       </c>
       <c r="F7" t="n">
-        <v>3736.8</v>
+        <v>5313.6</v>
       </c>
       <c r="G7" t="n">
-        <v>4673.487665886038</v>
+        <v>9622.454013613662</v>
       </c>
       <c r="H7" t="n">
-        <v>8410.287665886037</v>
+        <v>14936.05401361366</v>
       </c>
       <c r="I7" t="n">
         <v>5000</v>
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>16830.68287943381</v>
+        <v>19395.96364649746</v>
       </c>
       <c r="L7" t="n">
         <v>0.05</v>
@@ -851,13 +851,13 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>79.39508302539429</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>57.92667956937272</v>
+        <v>81.13625363186617</v>
       </c>
       <c r="P7" t="n">
-        <v>8.927597921540723</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>60</v>
@@ -879,19 +879,19 @@
         <v>0.3</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3845448868032644</v>
+        <v>0.4996792370830447</v>
       </c>
       <c r="E8" t="n">
-        <v>67074.19337427949</v>
+        <v>28538.14410235422</v>
       </c>
       <c r="F8" t="n">
-        <v>3736.8</v>
+        <v>5313.6</v>
       </c>
       <c r="G8" t="n">
-        <v>4673.487665886038</v>
+        <v>9622.454013613653</v>
       </c>
       <c r="H8" t="n">
-        <v>8410.287665886037</v>
+        <v>14936.05401361365</v>
       </c>
       <c r="I8" t="n">
         <v>5000</v>
@@ -900,7 +900,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>16830.68287943382</v>
+        <v>18854.30012709035</v>
       </c>
       <c r="L8" t="n">
         <v>0.05</v>
@@ -909,13 +909,13 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>79.39508302539429</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>57.92667956937272</v>
+        <v>69.54536025588556</v>
       </c>
       <c r="P8" t="n">
-        <v>8.927597921540723</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>60</v>
@@ -937,19 +937,19 @@
         <v>0.3</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3845448868032644</v>
+        <v>0.4929336602464435</v>
       </c>
       <c r="E9" t="n">
-        <v>67074.19337427949</v>
+        <v>25060.87608955989</v>
       </c>
       <c r="F9" t="n">
-        <v>3736.8</v>
+        <v>5313.6</v>
       </c>
       <c r="G9" t="n">
-        <v>4673.487665886038</v>
+        <v>9622.45401361366</v>
       </c>
       <c r="H9" t="n">
-        <v>8410.287665886037</v>
+        <v>14936.05401361366</v>
       </c>
       <c r="I9" t="n">
         <v>5000</v>
@@ -958,7 +958,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>16830.68287943381</v>
+        <v>18448.05248753502</v>
       </c>
       <c r="L9" t="n">
         <v>0.05</v>
@@ -967,13 +967,13 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>79.39508302539429</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>57.92667956937272</v>
+        <v>60.85219022389972</v>
       </c>
       <c r="P9" t="n">
-        <v>8.927597921540723</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>60</v>
@@ -995,19 +995,19 @@
         <v>0.3</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3845448868032644</v>
+        <v>0.4876871004846423</v>
       </c>
       <c r="E10" t="n">
-        <v>67074.19337427949</v>
+        <v>22356.33430183103</v>
       </c>
       <c r="F10" t="n">
-        <v>3736.8</v>
+        <v>5313.6</v>
       </c>
       <c r="G10" t="n">
-        <v>4673.487665886038</v>
+        <v>9622.454013613657</v>
       </c>
       <c r="H10" t="n">
-        <v>8410.287665886037</v>
+        <v>14936.05401361366</v>
       </c>
       <c r="I10" t="n">
         <v>5000</v>
@@ -1016,7 +1016,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>16830.68287943381</v>
+        <v>18132.08210121421</v>
       </c>
       <c r="L10" t="n">
         <v>0.05</v>
@@ -1025,13 +1025,13 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>79.39508302539429</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>57.92667956937272</v>
+        <v>54.09083575457758</v>
       </c>
       <c r="P10" t="n">
-        <v>8.927597921540723</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>60</v>
